--- a/katsunami_menu_data.xlsx
+++ b/katsunami_menu_data.xlsx
@@ -522,7 +522,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scraped: 15 April 2026, 10:52 WIB  |  Source: GrabFood  |  ID: 6-C7EYGBJDME3JRN</t>
+          <t>Scraped: 15 April 2026, 10:54 WIB  |  Source: GrabFood  |  ID: 6-C7EYGBJDME3JRN</t>
         </is>
       </c>
     </row>
